--- a/Team-Data/2013-14/2-24-2013-14.xlsx
+++ b/Team-Data/2013-14/2-24-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" t="n">
         <v>19</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
@@ -870,31 +937,31 @@
         <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.326</v>
+        <v>0.327</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P3" t="n">
         <v>21.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.766</v>
+        <v>0.762</v>
       </c>
       <c r="R3" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="U3" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V3" t="n">
         <v>15.4</v>
@@ -906,25 +973,25 @@
         <v>4.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB3" t="n">
         <v>95.09999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.9</v>
+        <v>-3.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF3" t="n">
         <v>27</v>
@@ -942,7 +1009,7 @@
         <v>11</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
@@ -963,22 +1030,22 @@
         <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
         <v>26</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
         <v>18</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -1154,13 +1221,13 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV4" t="n">
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>15</v>
@@ -1297,7 +1364,7 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI5" t="n">
         <v>27</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1336,7 +1403,7 @@
         <v>21</v>
       </c>
       <c r="AU5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1491,7 +1558,7 @@
         <v>28</v>
       </c>
       <c r="AL6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM6" t="n">
         <v>27</v>
@@ -1509,7 +1576,7 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1521,7 +1588,7 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW6" t="n">
         <v>22</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>22</v>
@@ -1670,7 +1737,7 @@
         <v>5</v>
       </c>
       <c r="AK7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL7" t="n">
         <v>20</v>
@@ -1679,10 +1746,10 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP7" t="n">
         <v>15</v>
@@ -1706,7 +1773,7 @@
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -1753,22 +1820,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8" t="n">
         <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>0.603</v>
+        <v>0.596</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J8" t="n">
         <v>83.40000000000001</v>
@@ -1777,37 +1844,37 @@
         <v>0.473</v>
       </c>
       <c r="L8" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O8" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q8" t="n">
         <v>0.801</v>
       </c>
       <c r="R8" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="T8" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U8" t="n">
         <v>23.7</v>
       </c>
       <c r="V8" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W8" t="n">
         <v>8.699999999999999</v>
@@ -1825,13 +1892,13 @@
         <v>19.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.5</v>
+        <v>104.4</v>
       </c>
       <c r="AC8" t="n">
         <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1840,7 +1907,7 @@
         <v>10</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
         <v>29</v>
@@ -1855,7 +1922,7 @@
         <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
@@ -1864,7 +1931,7 @@
         <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP8" t="n">
         <v>24</v>
@@ -1876,7 +1943,7 @@
         <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
         <v>28</v>
@@ -1888,7 +1955,7 @@
         <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
         <v>24</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2034,10 +2101,10 @@
         <v>7</v>
       </c>
       <c r="AK9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2049,7 +2116,7 @@
         <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
         <v>27</v>
@@ -2067,7 +2134,7 @@
         <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW9" t="n">
         <v>23</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>0.404</v>
+        <v>0.411</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,25 +2202,25 @@
         <v>38.8</v>
       </c>
       <c r="J10" t="n">
-        <v>86.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N10" t="n">
         <v>0.312</v>
       </c>
       <c r="O10" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="n">
         <v>0.662</v>
@@ -2168,10 +2235,10 @@
         <v>45</v>
       </c>
       <c r="U10" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W10" t="n">
         <v>8.800000000000001</v>
@@ -2183,19 +2250,19 @@
         <v>4.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA10" t="n">
         <v>20.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
@@ -2207,7 +2274,7 @@
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>7</v>
@@ -2219,19 +2286,19 @@
         <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN10" t="n">
         <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2240,13 +2307,13 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV10" t="n">
         <v>17</v>
@@ -2255,7 +2322,7 @@
         <v>3</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
@@ -2264,7 +2331,7 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11" t="n">
         <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>0.614</v>
+        <v>0.607</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
@@ -2317,19 +2384,19 @@
         <v>38.9</v>
       </c>
       <c r="J11" t="n">
-        <v>85</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0.457</v>
       </c>
       <c r="L11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M11" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.379</v>
+        <v>0.378</v>
       </c>
       <c r="O11" t="n">
         <v>16.3</v>
@@ -2338,10 +2405,10 @@
         <v>21.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="R11" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S11" t="n">
         <v>34.6</v>
@@ -2353,19 +2420,19 @@
         <v>22.8</v>
       </c>
       <c r="V11" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W11" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X11" t="n">
         <v>5.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
         <v>19.9</v>
@@ -2374,10 +2441,10 @@
         <v>103.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,7 +2456,7 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
@@ -2401,7 +2468,7 @@
         <v>9</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
@@ -2431,10 +2498,10 @@
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
@@ -2571,7 +2638,7 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI12" t="n">
         <v>15</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>7.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2771,7 +2838,7 @@
         <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
@@ -2792,7 +2859,7 @@
         <v>4</v>
       </c>
       <c r="AU13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -2845,37 +2912,37 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.661</v>
+        <v>0.655</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="J14" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="M14" t="n">
         <v>23.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.349</v>
+        <v>0.345</v>
       </c>
       <c r="O14" t="n">
         <v>21.9</v>
@@ -2884,7 +2951,7 @@
         <v>30.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.728</v>
+        <v>0.727</v>
       </c>
       <c r="R14" t="n">
         <v>10.4</v>
@@ -2893,34 +2960,34 @@
         <v>32.6</v>
       </c>
       <c r="T14" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U14" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="V14" t="n">
         <v>13.9</v>
       </c>
       <c r="W14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X14" t="n">
         <v>4.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="AA14" t="n">
         <v>24.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.3</v>
+        <v>107.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -2947,13 +3014,13 @@
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO14" t="n">
         <v>1</v>
@@ -2962,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -3105,10 +3172,10 @@
         <v>-5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF15" t="n">
         <v>26</v>
@@ -3126,13 +3193,13 @@
         <v>10</v>
       </c>
       <c r="AK15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM15" t="n">
         <v>5</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>6</v>
       </c>
       <c r="AN15" t="n">
         <v>8</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3335,7 +3402,7 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3359,7 +3426,7 @@
         <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC16" t="n">
         <v>13</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3566,7 @@
         <v>13</v>
       </c>
       <c r="AN17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO17" t="n">
         <v>13</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
         <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>0.196</v>
+        <v>0.182</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
       </c>
       <c r="I18" t="n">
-        <v>35.2</v>
+        <v>35</v>
       </c>
       <c r="J18" t="n">
         <v>82.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.426</v>
+        <v>0.423</v>
       </c>
       <c r="L18" t="n">
         <v>7.3</v>
@@ -3603,31 +3670,31 @@
         <v>20.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.355</v>
+        <v>0.351</v>
       </c>
       <c r="O18" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P18" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="Q18" t="n">
         <v>0.751</v>
       </c>
       <c r="R18" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="S18" t="n">
         <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U18" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="V18" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="W18" t="n">
         <v>6.8</v>
@@ -3642,16 +3709,16 @@
         <v>20.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.800000000000001</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3672,7 +3739,7 @@
         <v>16</v>
       </c>
       <c r="AK18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL18" t="n">
         <v>18</v>
@@ -3681,10 +3748,10 @@
         <v>17</v>
       </c>
       <c r="AN18" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AO18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP18" t="n">
         <v>27</v>
@@ -3693,7 +3760,7 @@
         <v>20</v>
       </c>
       <c r="AR18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS18" t="n">
         <v>29</v>
@@ -3702,10 +3769,10 @@
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>3.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE19" t="n">
         <v>15</v>
@@ -3845,7 +3912,7 @@
         <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
         <v>10</v>
@@ -3863,7 +3930,7 @@
         <v>12</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3890,7 +3957,7 @@
         <v>7</v>
       </c>
       <c r="AW19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -3937,22 +4004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" t="n">
         <v>23</v>
       </c>
       <c r="F20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20" t="n">
-        <v>0.411</v>
+        <v>0.418</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
         <v>83.40000000000001</v>
@@ -3961,40 +4028,40 @@
         <v>0.455</v>
       </c>
       <c r="L20" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N20" t="n">
         <v>0.384</v>
       </c>
       <c r="O20" t="n">
-        <v>17.4</v>
+        <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.766</v>
+        <v>0.764</v>
       </c>
       <c r="R20" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S20" t="n">
         <v>30.3</v>
       </c>
       <c r="T20" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U20" t="n">
         <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="W20" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X20" t="n">
         <v>6.4</v>
@@ -4006,16 +4073,16 @@
         <v>22.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1.9</v>
+        <v>-1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4027,7 +4094,7 @@
         <v>20</v>
       </c>
       <c r="AH20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI20" t="n">
         <v>13</v>
@@ -4048,7 +4115,7 @@
         <v>2</v>
       </c>
       <c r="AO20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AP20" t="n">
         <v>18</v>
@@ -4057,19 +4124,19 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS20" t="n">
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AU20" t="n">
         <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>11</v>
@@ -4084,7 +4151,7 @@
         <v>27</v>
       </c>
       <c r="BA20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" t="n">
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
-        <v>0.368</v>
+        <v>0.375</v>
       </c>
       <c r="H21" t="n">
         <v>48.6</v>
@@ -4137,28 +4204,28 @@
         <v>37</v>
       </c>
       <c r="J21" t="n">
-        <v>83.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.446</v>
+        <v>0.444</v>
       </c>
       <c r="L21" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="M21" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="O21" t="n">
         <v>14.7</v>
       </c>
       <c r="P21" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.748</v>
+        <v>0.746</v>
       </c>
       <c r="R21" t="n">
         <v>10.8</v>
@@ -4170,16 +4237,16 @@
         <v>40.7</v>
       </c>
       <c r="U21" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V21" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="W21" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y21" t="n">
         <v>3.7</v>
@@ -4191,19 +4258,19 @@
         <v>19.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="AC21" t="n">
         <v>-1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG21" t="n">
         <v>23</v>
@@ -4218,16 +4285,16 @@
         <v>14</v>
       </c>
       <c r="AK21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
       </c>
       <c r="AM21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4248,13 +4315,13 @@
         <v>26</v>
       </c>
       <c r="AU21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV21" t="n">
         <v>2</v>
       </c>
       <c r="AW21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX21" t="n">
         <v>19</v>
@@ -4266,13 +4333,13 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4591,7 +4658,7 @@
         <v>21</v>
       </c>
       <c r="AN23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO23" t="n">
         <v>23</v>
@@ -4612,13 +4679,13 @@
         <v>23</v>
       </c>
       <c r="AU23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV23" t="n">
         <v>12</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
         <v>25</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E24" t="n">
         <v>15</v>
       </c>
       <c r="F24" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G24" t="n">
-        <v>0.263</v>
+        <v>0.268</v>
       </c>
       <c r="H24" t="n">
         <v>48.6</v>
       </c>
       <c r="I24" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J24" t="n">
         <v>88.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L24" t="n">
         <v>6.8</v>
@@ -4695,10 +4762,10 @@
         <v>21.9</v>
       </c>
       <c r="N24" t="n">
-        <v>0.311</v>
+        <v>0.31</v>
       </c>
       <c r="O24" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P24" t="n">
         <v>23.4</v>
@@ -4710,25 +4777,25 @@
         <v>12</v>
       </c>
       <c r="S24" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="T24" t="n">
-        <v>44</v>
+        <v>44.3</v>
       </c>
       <c r="U24" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V24" t="n">
         <v>17.4</v>
       </c>
       <c r="W24" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="X24" t="n">
         <v>4</v>
       </c>
       <c r="Y24" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="Z24" t="n">
         <v>21.8</v>
@@ -4737,19 +4804,19 @@
         <v>20.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>100.4</v>
+        <v>100.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>-10.6</v>
+        <v>-10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
       </c>
       <c r="AF24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG24" t="n">
         <v>29</v>
@@ -4764,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4785,7 +4852,7 @@
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>3.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4934,7 +5001,7 @@
         <v>8</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH25" t="n">
         <v>19</v>
@@ -4955,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -5107,10 +5174,10 @@
         <v>4.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
@@ -5119,7 +5186,7 @@
         <v>5</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5134,7 +5201,7 @@
         <v>3</v>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
         <v>3</v>
@@ -5161,7 +5228,7 @@
         <v>5</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
@@ -5170,7 +5237,7 @@
         <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-1.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
         <v>24</v>
@@ -5313,13 +5380,13 @@
         <v>17</v>
       </c>
       <c r="AL27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN27" t="n">
         <v>23</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>24</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>5.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5504,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="AO28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP28" t="n">
         <v>29</v>
@@ -5519,7 +5586,7 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5674,10 +5741,10 @@
         <v>18</v>
       </c>
       <c r="AK29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
@@ -5701,10 +5768,10 @@
         <v>21</v>
       </c>
       <c r="AT29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -5757,34 +5824,34 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" t="n">
         <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.357</v>
+        <v>0.345</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="J30" t="n">
         <v>81.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="L30" t="n">
         <v>6.6</v>
       </c>
       <c r="M30" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N30" t="n">
         <v>0.349</v>
@@ -5796,19 +5863,19 @@
         <v>21.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R30" t="n">
         <v>10.9</v>
       </c>
       <c r="S30" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T30" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U30" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V30" t="n">
         <v>14.6</v>
@@ -5817,7 +5884,7 @@
         <v>6.9</v>
       </c>
       <c r="X30" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y30" t="n">
         <v>4.8</v>
@@ -5829,22 +5896,22 @@
         <v>20.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-5.8</v>
+        <v>-6.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF30" t="n">
         <v>24</v>
       </c>
-      <c r="AF30" t="n">
-        <v>23</v>
-      </c>
       <c r="AG30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
@@ -5856,7 +5923,7 @@
         <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL30" t="n">
         <v>23</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
         <v>22</v>
@@ -5907,7 +5974,7 @@
         <v>16</v>
       </c>
       <c r="BB30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6056,7 +6123,7 @@
         <v>26</v>
       </c>
       <c r="AQ31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR31" t="n">
         <v>19</v>
@@ -6065,7 +6132,7 @@
         <v>19</v>
       </c>
       <c r="AT31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU31" t="n">
         <v>8</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-24-2013-14</t>
+          <t>2014-02-24</t>
         </is>
       </c>
     </row>
